--- a/outputs/monitor_xlsx/20260224.xlsx
+++ b/outputs/monitor_xlsx/20260224.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2368,13 +2368,13 @@
         <v>1172</v>
       </c>
       <c r="L26" t="n">
-        <v>4767</v>
+        <v>3869</v>
       </c>
       <c r="M26" t="n">
         <v>-106282</v>
       </c>
       <c r="N26" t="n">
-        <v>17.86</v>
+        <v>15.24</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2432,6 +2432,59 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4765</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E28" t="n">
+        <v>569</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-176</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-64</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K28" t="n">
+        <v>363</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1737</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-8884</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260224.xlsx
+++ b/outputs/monitor_xlsx/20260224.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>34700.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
+          <t>+2.75%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5171.4$</t>
+          <t>311.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.64%</t>
-        </is>
-      </c>
+          <t>+2.50%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>34827.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26%</t>
-        </is>
-      </c>
+          <t>+2.52%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8332.34</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+1.45%</t>
-        </is>
-      </c>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>5155.8$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-6.95%</t>
-        </is>
-      </c>
+          <t>-0.94%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>627.34億</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>407.85億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2039.25億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>39.49億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>789.83億</t>
-        </is>
-      </c>
+          <t>31.43</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.26%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>61.59億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>27.63億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>138.16億</t>
-        </is>
-      </c>
+          <t>8332.34</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+1.45%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>176.41%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>171.94%</t>
-        </is>
-      </c>
+          <t>19.55</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-6.95%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>842.41億</t>
-        </is>
-      </c>
+          <t>65.63$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-1.03%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,52 +765,173 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9753口</t>
-        </is>
-      </c>
+          <t>627.34億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>282.12億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1410.61億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>61.59億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>31.83億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>159.15億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>842.41億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9753口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>13015口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-55.39億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-15.12億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-75.59億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-12.8億</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>-255.98億</t>
         </is>
@@ -838,7 +980,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>407.85億</t>
+          <t>282.12億</t>
         </is>
       </c>
     </row>
@@ -850,7 +992,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2039.25億</t>
+          <t>1410.61億</t>
         </is>
       </c>
     </row>
@@ -862,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>39.49億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -874,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>789.83億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -886,7 +1032,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27.63億</t>
+          <t>31.83億</t>
         </is>
       </c>
     </row>
@@ -898,7 +1044,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>138.16億</t>
+          <t>159.15億</t>
         </is>
       </c>
     </row>
@@ -972,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>171.94%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -984,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>13015口</t>
         </is>
       </c>
     </row>
@@ -999,20 +1145,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -1033,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1047,67 +1192,67 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>市場別</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>漲跌幅(%)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>成交量(張)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>外資當日(張)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>外資5日累計</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>投信當日(張)</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>投信5日累計</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>自營商當日(張)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>融資增減(張)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>融資5日累計</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>借券增減(張)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>MA20乖離(%)</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>籌碼評價</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
@@ -1157,43 +1302,43 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>2.58</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>150367</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>-37083</v>
       </c>
-      <c r="G4" t="n">
-        <v>-61521</v>
-      </c>
       <c r="H4" t="n">
+        <v>-179</v>
+      </c>
+      <c r="I4" t="n">
         <v>9000</v>
       </c>
-      <c r="I4" t="n">
-        <v>7700</v>
-      </c>
       <c r="J4" t="n">
+        <v>22926</v>
+      </c>
+      <c r="K4" t="n">
         <v>37123</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7584</v>
       </c>
-      <c r="L4" t="n">
-        <v>7621</v>
-      </c>
       <c r="M4" t="n">
+        <v>29440</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4064925</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1204,39 +1349,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>-241</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-111</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>956</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3385</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-213</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1047</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J5" t="n">
-        <v>1693</v>
+        <v>-1166</v>
       </c>
       <c r="K5" t="n">
-        <v>9830</v>
+        <v>168</v>
       </c>
       <c r="L5" t="n">
-        <v>10145</v>
+        <v>3010</v>
       </c>
       <c r="M5" t="n">
-        <v>-28282</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
+        <v>11451</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-78765</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1247,51 +1404,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>956</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3385</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>-213</v>
-      </c>
-      <c r="G6" t="n">
-        <v>144</v>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1385</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14083</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>1949</v>
       </c>
       <c r="H6" t="n">
-        <v>72</v>
+        <v>1801</v>
       </c>
       <c r="I6" t="n">
-        <v>-589</v>
+        <v>312</v>
       </c>
       <c r="J6" t="n">
-        <v>168</v>
+        <v>1498</v>
       </c>
       <c r="K6" t="n">
-        <v>3010</v>
+        <v>149</v>
       </c>
       <c r="L6" t="n">
-        <v>2872</v>
+        <v>6655</v>
       </c>
       <c r="M6" t="n">
-        <v>-78765</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+        <v>25323</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-648614</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1302,51 +1459,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>華新</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E7" t="n">
-        <v>60522</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>-5110</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-836</v>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1965</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44316</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>6887</v>
       </c>
       <c r="H7" t="n">
-        <v>-76</v>
+        <v>-6947</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1486</v>
       </c>
       <c r="J7" t="n">
-        <v>519</v>
+        <v>3970</v>
       </c>
       <c r="K7" t="n">
-        <v>82771</v>
+        <v>337</v>
       </c>
       <c r="L7" t="n">
-        <v>75499</v>
+        <v>21095</v>
       </c>
       <c r="M7" t="n">
-        <v>-1105287</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
+        <v>87310</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-6482900</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1357,51 +1514,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>1385</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="E8" t="n">
-        <v>14083</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1949</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1710</v>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3441</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>197</v>
       </c>
       <c r="H8" t="n">
-        <v>312</v>
+        <v>3402</v>
       </c>
       <c r="I8" t="n">
-        <v>766</v>
+        <v>58</v>
       </c>
       <c r="J8" t="n">
-        <v>149</v>
+        <v>1756</v>
       </c>
       <c r="K8" t="n">
-        <v>6655</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
-        <v>6544</v>
+        <v>1774</v>
       </c>
       <c r="M8" t="n">
-        <v>-648614</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>8564</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-140144</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1412,51 +1569,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1965</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44316</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>6887</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-17559</v>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1225</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5073</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-697</v>
       </c>
       <c r="H9" t="n">
-        <v>1486</v>
+        <v>752</v>
       </c>
       <c r="I9" t="n">
-        <v>2322</v>
+        <v>474</v>
       </c>
       <c r="J9" t="n">
-        <v>337</v>
+        <v>-145</v>
       </c>
       <c r="K9" t="n">
-        <v>21095</v>
+        <v>83</v>
       </c>
       <c r="L9" t="n">
-        <v>21832</v>
+        <v>1172</v>
       </c>
       <c r="M9" t="n">
-        <v>-6482900</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+        <v>3595</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-106282</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1467,51 +1624,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>122</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="E10" t="n">
-        <v>249188</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>-22945</v>
-      </c>
-      <c r="G10" t="n">
-        <v>19585</v>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3773</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>10171</v>
+        <v>-1009</v>
       </c>
       <c r="I10" t="n">
-        <v>5327</v>
+        <v>503</v>
       </c>
       <c r="J10" t="n">
-        <v>1440</v>
+        <v>1141</v>
       </c>
       <c r="K10" t="n">
-        <v>145498</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>133659</v>
+        <v>2218</v>
       </c>
       <c r="M10" t="n">
-        <v>-1110890</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>8674</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-89471</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1522,51 +1679,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2310</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3773</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-245</v>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>918</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>36</v>
       </c>
       <c r="H11" t="n">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>2218</v>
+        <v>28</v>
       </c>
       <c r="L11" t="n">
-        <v>2223</v>
+        <v>4239</v>
       </c>
       <c r="M11" t="n">
-        <v>-89471</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+        <v>16890</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-19168</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1577,51 +1734,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>3430</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2196</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>494</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-226</v>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4765</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F12" t="n">
+        <v>569</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>29</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>-205</v>
       </c>
       <c r="I12" t="n">
-        <v>-109</v>
+        <v>-18</v>
       </c>
       <c r="J12" t="n">
-        <v>78</v>
+        <v>-46</v>
       </c>
       <c r="K12" t="n">
-        <v>5835</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>5935</v>
+        <v>363</v>
       </c>
       <c r="M12" t="n">
-        <v>-19717</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
+        <v>1374</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-8884</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1632,51 +1789,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>211.5</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="E13" t="n">
-        <v>42932</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>-5613</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4524</v>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2315</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>963</v>
+        <v>-146</v>
       </c>
       <c r="I13" t="n">
-        <v>1530</v>
+        <v>-71</v>
       </c>
       <c r="J13" t="n">
-        <v>619</v>
+        <v>186</v>
       </c>
       <c r="K13" t="n">
-        <v>24191</v>
+        <v>-52</v>
       </c>
       <c r="L13" t="n">
-        <v>24133</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>-267278</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>-145</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1687,51 +1844,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>光聖</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2030</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="E14" t="n">
-        <v>918</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="G14" t="n">
-        <v>27</v>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3871</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1009</v>
       </c>
       <c r="H14" t="n">
-        <v>35</v>
+        <v>1507</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="J14" t="n">
-        <v>28</v>
+        <v>2330</v>
       </c>
       <c r="K14" t="n">
-        <v>4239</v>
+        <v>73</v>
       </c>
       <c r="L14" t="n">
-        <v>4215</v>
+        <v>-171</v>
       </c>
       <c r="M14" t="n">
-        <v>-19168</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>-914</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1742,51 +1899,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1265</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>608</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-173</v>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>3471</v>
       </c>
       <c r="H15" t="n">
-        <v>-71</v>
-      </c>
-      <c r="I15" t="n">
-        <v>113</v>
+        <v>6027</v>
       </c>
       <c r="J15" t="n">
-        <v>-52</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="L15" t="n">
-        <v>-22</v>
+        <v>-100</v>
       </c>
       <c r="M15" t="n">
+        <v>-389</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1797,694 +1951,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>313</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>13484</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>1720</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1899</v>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F16" t="n">
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-48</v>
       </c>
       <c r="H16" t="n">
-        <v>-486</v>
-      </c>
-      <c r="I16" t="n">
-        <v>568</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>169</v>
+        <v>-85</v>
       </c>
       <c r="K16" t="n">
-        <v>-786</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>498</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
+        <v>-39</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>台新科</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2027</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>304</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1104</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-80</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-39</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>393</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16451</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>1009</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3379</v>
-      </c>
-      <c r="H18" t="n">
-        <v>205</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1747</v>
-      </c>
-      <c r="J18" t="n">
-        <v>73</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-171</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-404</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>321</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="E19" t="n">
-        <v>34019</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>-33</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-903</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1027</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>986</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20107</v>
-      </c>
-      <c r="L19" t="n">
-        <v>20200</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-112988</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3835</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1529</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-69</v>
-      </c>
-      <c r="G20" t="n">
-        <v>282</v>
-      </c>
-      <c r="H20" t="n">
-        <v>83</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-150</v>
-      </c>
-      <c r="J20" t="n">
-        <v>45</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2120</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11864</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-46413</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>179.5</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7621</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>-477</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-1219</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>27</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4625</v>
-      </c>
-      <c r="L21" t="n">
-        <v>21573</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-11383</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>980</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2455</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>210</v>
-      </c>
-      <c r="G22" t="n">
-        <v>612</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-226</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-477</v>
-      </c>
-      <c r="J22" t="n">
-        <v>93</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2435</v>
-      </c>
-      <c r="L22" t="n">
-        <v>12181</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-47589</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1405</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E23" t="n">
-        <v>3441</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>197</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3599</v>
-      </c>
-      <c r="H23" t="n">
-        <v>58</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1814</v>
-      </c>
-      <c r="J23" t="n">
-        <v>32</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1774</v>
-      </c>
-      <c r="L23" t="n">
-        <v>10338</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-140144</v>
-      </c>
-      <c r="N23" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>962</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-48</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-22</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-85</v>
-      </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>17</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-22</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>3471</v>
-      </c>
-      <c r="G25" t="n">
-        <v>9498</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>149</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-489</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1225</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="E26" t="n">
-        <v>5073</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-697</v>
-      </c>
-      <c r="G26" t="n">
-        <v>54</v>
-      </c>
-      <c r="H26" t="n">
-        <v>474</v>
-      </c>
-      <c r="I26" t="n">
-        <v>328</v>
-      </c>
-      <c r="J26" t="n">
-        <v>83</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1172</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3869</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-106282</v>
-      </c>
-      <c r="N26" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>203</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4962</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>483</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2251</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" t="n">
-        <v>230</v>
-      </c>
-      <c r="K27" t="n">
-        <v>6225</v>
-      </c>
-      <c r="L27" t="n">
-        <v>29499</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-58876</v>
-      </c>
-      <c r="N27" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4765</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="E28" t="n">
-        <v>569</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-176</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-64</v>
-      </c>
-      <c r="J28" t="n">
-        <v>15</v>
-      </c>
-      <c r="K28" t="n">
-        <v>363</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1737</v>
-      </c>
-      <c r="M28" t="n">
-        <v>-8884</v>
-      </c>
-      <c r="N28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260224.xlsx
+++ b/outputs/monitor_xlsx/20260224.xlsx
@@ -544,10 +544,6 @@
           <t>+2.75%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+2.50%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+2.52%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.02%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.94%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.26%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.45%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-6.95%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-1.03%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>627.34億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>282.12億</t>
@@ -811,7 +774,6 @@
           <t>61.59億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>31.83億</t>
@@ -822,8 +784,6 @@
           <t>159.15億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>842.41億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>9753口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13015口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-55.39億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-15.12億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,51 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>292</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2736</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>492</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7354</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>738</v>
+      </c>
+      <c r="J17" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6567</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25036</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21372</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260224.xlsx
+++ b/outputs/monitor_xlsx/20260224.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.58</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>150367</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-37083</v>
       </c>
       <c r="H4" t="n">
-        <v>-179</v>
+        <v>-37262</v>
       </c>
       <c r="I4" t="n">
         <v>9000</v>
       </c>
       <c r="J4" t="n">
-        <v>22926</v>
+        <v>31926</v>
       </c>
       <c r="K4" t="n">
         <v>37123</v>
@@ -1279,11 +1278,14 @@
         <v>7584</v>
       </c>
       <c r="M4" t="n">
-        <v>29440</v>
+        <v>37024</v>
       </c>
       <c r="N4" t="n">
         <v>-4064925</v>
       </c>
+      <c r="O4" t="n">
+        <v>7.91</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>956</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>-1.04</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>3385</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>-213</v>
       </c>
       <c r="H5" t="n">
-        <v>1047</v>
+        <v>834</v>
       </c>
       <c r="I5" t="n">
         <v>72</v>
       </c>
       <c r="J5" t="n">
-        <v>-1166</v>
+        <v>-1094</v>
       </c>
       <c r="K5" t="n">
         <v>168</v>
@@ -1334,11 +1336,14 @@
         <v>3010</v>
       </c>
       <c r="M5" t="n">
-        <v>11451</v>
+        <v>14461</v>
       </c>
       <c r="N5" t="n">
         <v>-78765</v>
       </c>
+      <c r="O5" t="n">
+        <v>-2.98</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1385</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>6.13</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>14083</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1949</v>
       </c>
       <c r="H6" t="n">
-        <v>1801</v>
+        <v>3750</v>
       </c>
       <c r="I6" t="n">
         <v>312</v>
       </c>
       <c r="J6" t="n">
-        <v>1498</v>
+        <v>1810</v>
       </c>
       <c r="K6" t="n">
         <v>149</v>
@@ -1389,11 +1394,14 @@
         <v>6655</v>
       </c>
       <c r="M6" t="n">
-        <v>25323</v>
+        <v>31978</v>
       </c>
       <c r="N6" t="n">
         <v>-648614</v>
       </c>
+      <c r="O6" t="n">
+        <v>13.76</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1965</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>3.42</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>44316</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>6887</v>
       </c>
       <c r="H7" t="n">
-        <v>-6947</v>
+        <v>-60</v>
       </c>
       <c r="I7" t="n">
         <v>1486</v>
       </c>
       <c r="J7" t="n">
-        <v>3970</v>
+        <v>5456</v>
       </c>
       <c r="K7" t="n">
         <v>337</v>
@@ -1444,11 +1452,14 @@
         <v>21095</v>
       </c>
       <c r="M7" t="n">
-        <v>87310</v>
+        <v>108405</v>
       </c>
       <c r="N7" t="n">
         <v>-6482900</v>
       </c>
+      <c r="O7" t="n">
+        <v>8.83</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1405</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0.36</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>3441</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>197</v>
       </c>
       <c r="H8" t="n">
-        <v>3402</v>
+        <v>3599</v>
       </c>
       <c r="I8" t="n">
         <v>58</v>
       </c>
       <c r="J8" t="n">
-        <v>1756</v>
+        <v>1814</v>
       </c>
       <c r="K8" t="n">
         <v>32</v>
@@ -1499,11 +1510,14 @@
         <v>1774</v>
       </c>
       <c r="M8" t="n">
-        <v>8564</v>
+        <v>10338</v>
       </c>
       <c r="N8" t="n">
         <v>-140144</v>
       </c>
+      <c r="O8" t="n">
+        <v>15.35</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1225</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>6.06</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>5073</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-697</v>
       </c>
       <c r="H9" t="n">
-        <v>752</v>
+        <v>54</v>
       </c>
       <c r="I9" t="n">
         <v>474</v>
       </c>
       <c r="J9" t="n">
-        <v>-145</v>
+        <v>328</v>
       </c>
       <c r="K9" t="n">
         <v>83</v>
@@ -1554,11 +1568,14 @@
         <v>1172</v>
       </c>
       <c r="M9" t="n">
-        <v>3595</v>
+        <v>4767</v>
       </c>
       <c r="N9" t="n">
         <v>-106282</v>
       </c>
+      <c r="O9" t="n">
+        <v>19.09</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2310</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>6.21</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>3773</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>-1009</v>
+        <v>-999</v>
       </c>
       <c r="I10" t="n">
         <v>503</v>
       </c>
       <c r="J10" t="n">
-        <v>1141</v>
+        <v>1644</v>
       </c>
       <c r="K10" t="n">
         <v>56</v>
@@ -1609,11 +1626,14 @@
         <v>2218</v>
       </c>
       <c r="M10" t="n">
-        <v>8674</v>
+        <v>10892</v>
       </c>
       <c r="N10" t="n">
         <v>-89471</v>
       </c>
+      <c r="O10" t="n">
+        <v>22.77</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>2030</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>-0.25</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>918</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>36</v>
       </c>
       <c r="H11" t="n">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="I11" t="n">
         <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="K11" t="n">
         <v>28</v>
@@ -1664,11 +1684,14 @@
         <v>4239</v>
       </c>
       <c r="M11" t="n">
-        <v>16890</v>
+        <v>21129</v>
       </c>
       <c r="N11" t="n">
         <v>-19168</v>
       </c>
+      <c r="O11" t="n">
+        <v>23.35</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>4765</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>1.49</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>569</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>29</v>
       </c>
       <c r="H12" t="n">
-        <v>-205</v>
+        <v>-176</v>
       </c>
       <c r="I12" t="n">
         <v>-18</v>
       </c>
       <c r="J12" t="n">
-        <v>-46</v>
+        <v>-64</v>
       </c>
       <c r="K12" t="n">
         <v>15</v>
@@ -1719,11 +1742,14 @@
         <v>363</v>
       </c>
       <c r="M12" t="n">
-        <v>1374</v>
+        <v>1737</v>
       </c>
       <c r="N12" t="n">
         <v>-8884</v>
       </c>
+      <c r="O12" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>-146</v>
+        <v>-135</v>
       </c>
       <c r="I13" t="n">
         <v>-71</v>
       </c>
       <c r="J13" t="n">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="K13" t="n">
         <v>-52</v>
@@ -1774,11 +1800,14 @@
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1009</v>
       </c>
       <c r="H14" t="n">
-        <v>1507</v>
+        <v>2516</v>
       </c>
       <c r="I14" t="n">
         <v>205</v>
       </c>
       <c r="J14" t="n">
-        <v>2330</v>
+        <v>2535</v>
       </c>
       <c r="K14" t="n">
         <v>73</v>
@@ -1829,11 +1858,14 @@
         <v>-171</v>
       </c>
       <c r="M14" t="n">
-        <v>-914</v>
+        <v>-1085</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>3471</v>
       </c>
       <c r="H15" t="n">
-        <v>6027</v>
+        <v>9498</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1881,11 +1916,14 @@
         <v>-100</v>
       </c>
       <c r="M15" t="n">
-        <v>-389</v>
+        <v>-489</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-48</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>-22</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-85</v>
@@ -1933,11 +1974,14 @@
         <v>17</v>
       </c>
       <c r="M16" t="n">
-        <v>-39</v>
+        <v>-22</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,38 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>292</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>5.04</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>2736</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>492</v>
       </c>
-      <c r="G17" t="n">
-        <v>7354</v>
-      </c>
       <c r="H17" t="n">
+        <v>8883</v>
+      </c>
+      <c r="I17" t="n">
         <v>-5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>738</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>19</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6567</v>
       </c>
-      <c r="L17" t="n">
-        <v>25036</v>
-      </c>
       <c r="M17" t="n">
+        <v>31214</v>
+      </c>
+      <c r="N17" t="n">
         <v>-21372</v>
+      </c>
+      <c r="O17" t="n">
+        <v>24.53</v>
       </c>
     </row>
   </sheetData>
